--- a/attendance_report.xlsx
+++ b/attendance_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,11 +462,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nitin Bhati</t>
+          <t>Vinay Dhiman</t>
         </is>
       </c>
       <c r="C3" s="1" t="n">
@@ -488,9 +488,45 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
+        <v>46103</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nitin Bhati</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nitin Bhati</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46103</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
